--- a/customer_service_forms/004_customer_service_experience_feedback_form--customer_service_forms.xlsx
+++ b/customer_service_forms/004_customer_service_experience_feedback_form--customer_service_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_satisfied', 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_satisfied',_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_satisfied', 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_satisfied',_'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_satisfied', 'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'overall_quality',_'label':_'overall_quality'}</t>
+          <t>overall_quality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'overall_quality', 'label': 'Overall Quality'}</t>
+          <t>Overall Quality</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'response_time',_'label':_'response_time'}</t>
+          <t>response_time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'response_time', 'label': 'Response Time'}</t>
+          <t>Response Time</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'communication_skills',_'label':_'communication_skills'}</t>
+          <t>communication_skills</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'communication_skills', 'label': 'Communication Skills'}</t>
+          <t>Communication Skills</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'product_knowledge',_'label':_'product_knowledge'}</t>
+          <t>product_knowledge</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'product_knowledge', 'label': 'Product Knowledge'}</t>
+          <t>Product Knowledge</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good',_'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_good', 'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_good',_'label':_'somewhat_good'}</t>
+          <t>somewhat_good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'somewhat_good', 'label': 'Somewhat Good'}</t>
+          <t>Somewhat Good</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_good',_'label':_'not_good'}</t>
+          <t>not_good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_good', 'label': 'Not Good'}</t>
+          <t>Not Good</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'improve_response_time',_'label':_'improve_response_time'}</t>
+          <t>improve_response_time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'improve_response_time', 'label': 'Improve Response Time'}</t>
+          <t>Improve Response Time</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'improve_communication',_'label':_'improve_communication'}</t>
+          <t>improve_communication</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'improve_communication', 'label': 'Improve Communication'}</t>
+          <t>Improve Communication</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'improve_product_knowledge',_'label':_'improve_product_knowledge'}</t>
+          <t>improve_product_knowledge</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'improve_product_knowledge', 'label': 'Improve Product Knowledge'}</t>
+          <t>Improve Product Knowledge</t>
         </is>
       </c>
     </row>
